--- a/src/attributions/attributions_ig_traj_44.xlsx
+++ b/src/attributions/attributions_ig_traj_44.xlsx
@@ -2137,25 +2137,25 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.004470566670901355</v>
+        <v>0.004097445772040159</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2.808723864515988e-12</v>
+        <v>4.125717865317929e-12</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01617598433909159</v>
+        <v>0.02208089044849918</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2164,37 +2164,37 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009219254890988578</v>
+        <v>0.03407680999786797</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.002062664617296024</v>
+        <v>0.002608387215926132</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01670995202566579</v>
+        <v>-0.01988201473532345</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.006349871250817e-12</v>
+        <v>-2.073955543585209e-11</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001130477443023975</v>
+        <v>0.008385524173969278</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.004265792380273577</v>
+        <v>0.005637146491292612</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
@@ -2215,40 +2215,40 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01350227520382014</v>
+        <v>-0.04315637697537132</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01707006910579539</v>
+        <v>-0.03308147974915903</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.004099505244487858</v>
+        <v>-0.03341576396248269</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.0001658568290791305</v>
+        <v>0.001737397217819172</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01278036137384127</v>
+        <v>-0.02091044915903617</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.005659098355304363</v>
+        <v>-0.01622104155350271</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.05843923562803762</v>
+        <v>0.1598402475153808</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,10 +2284,10 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.0005836273332551345</v>
+        <v>-0.01222367860162013</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.03362676362710305</v>
+        <v>-0.03205045909150446</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,67 +2296,67 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01072994234332829</v>
+        <v>-0.007913758758893564</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.008722094646642045</v>
+        <v>-0.01209629544185139</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.006944686021135538</v>
+        <v>-0.009497391844476542</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02082607020883236</v>
+        <v>0.025472263569474</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002041225446696128</v>
+        <v>0.04734046345320434</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0105011295768715</v>
+        <v>0.05348833880895584</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.009251044242199314</v>
+        <v>0.01532393048397842</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.002472899739573181</v>
+        <v>-0.01421506524819196</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002773747129722149</v>
+        <v>-0.02234474669864295</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2380,37 +2380,37 @@
         <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.006694039320347771</v>
+        <v>-0.01477183742429348</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.007338037802521345</v>
+        <v>-0.006769637041035189</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.02529448927457532</v>
+        <v>0.03896371820904906</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.00919115834966416</v>
+        <v>-0.02426350282187236</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.008556610674094097</v>
+        <v>0.02756987466090194</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.002545434415264737</v>
+        <v>0.01998971308189605</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.003574193483520508</v>
+        <v>-0.01964422022113463</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
@@ -2446,37 +2446,37 @@
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.00850849896036329</v>
+        <v>-0.01101275129871497</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.02306645108412667</v>
+        <v>0.03615781586373699</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01805699667163302</v>
+        <v>-0.01542026414261989</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.003012005534221306</v>
+        <v>-0.01491535251392249</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.05220970833328708</v>
+        <v>0.008837070863466471</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,106 +2485,106 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.006266858715971099</v>
+        <v>-0.0007487500728723262</v>
       </c>
       <c r="DP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.007310014683442425</v>
+        <v>0.02158212774884324</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.005763503682034826</v>
+        <v>0.06177174489926076</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.002181577152156562</v>
+        <v>0.008053335337775568</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01423095511096748</v>
+        <v>-0.0118549248525404</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.02019964972397772</v>
+        <v>-0.03562824391112236</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
         <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.002627612131997236</v>
+        <v>-0.03044876676016381</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.004259486635148892</v>
+        <v>-0.03220955671043951</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.009373343230285439</v>
+        <v>0.007249336690297412</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.0002460819609258587</v>
+        <v>0.01378128931469118</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.00203745841780767</v>
+        <v>-0.01958625505498301</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.03538173816874376</v>
+        <v>0.02978767293229135</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.004833388596184912</v>
+        <v>-0.02210210726907485</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.006358309291867888</v>
+        <v>-0.01925299469072182</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.02216628546251967</v>
+        <v>0.03255903757770472</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.009271735440656258</v>
+        <v>-0.03366828677188718</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02136737175639945</v>
+        <v>-0.005394772737736113</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.003471785472516163</v>
+        <v>-0.01533201987862502</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.0003270642557242236</v>
+        <v>0.01485300223288186</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.005550808704736774</v>
+        <v>0.01314682772088162</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03761871723992512</v>
+        <v>0.02096221350664748</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,25 +2674,25 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02275153804349715</v>
+        <v>0.008836044050116638</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.003517930836090955</v>
+        <v>0.03193539066614511</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.08230255709418684</v>
+        <v>0.02606972680552399</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08141669680007123</v>
+        <v>-0.04597355031562213</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.002323062556888249</v>
+        <v>-0.002743171911561151</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2733,19 +2733,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1629682515574328</v>
+        <v>0.06555513582821686</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09711943394546009</v>
+        <v>-0.07680836238372205</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02557949019377585</v>
+        <v>-0.00971106990593721</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007491045650329808</v>
+        <v>-0.001473965928343202</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.01020032817251278</v>
+        <v>-0.006488968419062459</v>
       </c>
       <c r="W5" t="n">
-        <v>-3.7833047295284e-11</v>
+        <v>-4.119360135584861e-11</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,25 +2787,25 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07539364963578626</v>
+        <v>0.0377231954852617</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.05947728527694322</v>
+        <v>-0.02881353524081224</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0899494162877776</v>
+        <v>0.02230533788295849</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -2817,22 +2817,22 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0648087616550522</v>
+        <v>0.04946425631890088</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.08481256114425777</v>
+        <v>-0.07171567112083216</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.04402374635229772</v>
+        <v>0.02181865778512829</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.6736248856799217</v>
+        <v>0.230165196522942</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.1293474985099085</v>
+        <v>-0.1498961530735703</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1907797306491732</v>
+        <v>-0.04865185494880135</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,22 +2865,22 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.002596652713826287</v>
+        <v>-0.00268205249560756</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.04569928631220152</v>
+        <v>-0.0170948940848988</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.09290273584129036</v>
+        <v>-0.01344124309205805</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.03180841640489628</v>
+        <v>-0.01454097936840872</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.1123696644567652</v>
+        <v>-0.0005115052114429669</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1116323604038055</v>
+        <v>0.1026490873258707</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,22 +2925,22 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1331672843284116</v>
+        <v>0.03833978837517499</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.02921613442679246</v>
+        <v>0.02885415956018613</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.008795577424084393</v>
+        <v>-0.02142620365284091</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2949,19 +2949,19 @@
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1475710874393862</v>
+        <v>-0.08784547468227842</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.05344185354830051</v>
+        <v>0.06703601925692083</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.05421348539263494</v>
+        <v>0.01326729080309722</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2970,88 +2970,88 @@
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.04909263012801379</v>
+        <v>-0.05889154165517679</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.06616967592265223</v>
+        <v>0.06683885767740268</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.06474114156855956</v>
+        <v>0.023425323832635</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.147271012391901</v>
+        <v>-0.09362414332657601</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.08473456944663794</v>
+        <v>0.07210820313297291</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.00275241140917977</v>
+        <v>0.01312338552709465</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.004325046162230779</v>
+        <v>-0.003491428871906511</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.06935612478869578</v>
+        <v>0.01655262427278511</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.04783270684754053</v>
+        <v>-0.02924666113539669</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>-0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
@@ -3060,25 +3060,25 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.199967214033285</v>
+        <v>-0.04559205161290208</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.07483193530323694</v>
+        <v>0.02111936698369336</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.06732068010243747</v>
+        <v>-0.06689582166189351</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
@@ -3087,76 +3087,76 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.03129570664472894</v>
+        <v>0.03311423480399043</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.07899587818005976</v>
+        <v>0.1003965410412071</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.03579087978648584</v>
+        <v>0.01018774284069215</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.06641579886754709</v>
+        <v>-0.09409342671886735</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.002118806204563411</v>
+        <v>0.05649096748106687</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.07444109328676309</v>
+        <v>0.01563558500784672</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1757231477566852</v>
+        <v>-0.02232663116328272</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.1132091240096416</v>
+        <v>0.03419474492134449</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.01452673705716884</v>
+        <v>0.03835201974892229</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,46 +3165,46 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1518291761581464</v>
+        <v>-0.1079274499285749</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.09685531989087542</v>
+        <v>0.07721591228196008</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.04983489022357649</v>
+        <v>0.007906432548242701</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01117103801370277</v>
+        <v>-0.06124253978305069</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.1147715562213789</v>
+        <v>0.0308047811373012</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.02351500709383083</v>
+        <v>0.06067693910412186</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
@@ -3216,22 +3216,22 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.02762543760775933</v>
+        <v>0.05810736054236579</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.05883564638927547</v>
+        <v>0.1760929245931809</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.1275848057854966</v>
+        <v>-0.03170874576754043</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
@@ -3240,37 +3240,37 @@
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.0453911105917113</v>
+        <v>-0.09686716778527807</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.04104713703369257</v>
+        <v>-0.002614062750636654</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.008012528948664619</v>
+        <v>0.007396230698887102</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001820369414214985</v>
+        <v>0.003966957368838327</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009599948819114043</v>
+        <v>0.02456704196328071</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009201096176909269</v>
+        <v>0.03171705197465934</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,13 +3314,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0066567655790748</v>
+        <v>0.006473708930686625</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001077239152113251</v>
+        <v>-0.002084891122775107</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001094463144880011</v>
+        <v>-0.002550343791126127</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001388675298633243</v>
+        <v>-0.002475623096384303</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002944699368073779</v>
+        <v>0.0006327268548259692</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01672567964526741</v>
+        <v>-0.02115548258158652</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.004675736360289264</v>
+        <v>-0.03589761414457381</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0004043755213583823</v>
+        <v>-0.01770878768116949</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,34 +3386,34 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.006134154606534659</v>
+        <v>0.003825433128636364</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.007166862885724312</v>
+        <v>-0.003116136697266511</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.004164875580803183</v>
+        <v>-0.0154599285608273</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.06141671342134616</v>
+        <v>0.09616667551329192</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3422,25 +3422,25 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.009833761680319499</v>
+        <v>-0.009169846926421114</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01332099181231793</v>
+        <v>-0.02300211190980093</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.001112115339937907</v>
+        <v>-0.006495048549907828</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,52 +3449,52 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01462621374933804</v>
+        <v>-0.005937456388702397</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.000239160239619881</v>
+        <v>0.002834751655991628</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.01128375525545447</v>
+        <v>0.01718212354809875</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.007889365528135845</v>
+        <v>0.04163055092072149</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.008054527062345761</v>
+        <v>0.03004610520243776</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.009236057187576335</v>
+        <v>0.01143891898472303</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.002394257243293517</v>
+        <v>5.767184034791828e-05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.004637924969994048</v>
+        <v>-0.01427268766602297</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.004711604419526328</v>
+        <v>-0.0105242853387235</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,13 +3530,13 @@
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0001733994995967226</v>
+        <v>-0.004232902858164198</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.008208273630988199</v>
+        <v>0.02524917766866688</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,49 +3548,49 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.001602995564458658</v>
+        <v>-0.01816401004183752</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.005425828887958162</v>
+        <v>0.02346248471429553</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.008282512136660409</v>
+        <v>0.01585843593436834</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.001601777208271201</v>
+        <v>-0.01336610556161891</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.00213301893159</v>
+        <v>-0.004315230958049639</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01286061326506981</v>
+        <v>0.02013544147734875</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3599,22 +3599,22 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.00330202675003722</v>
+        <v>-0.005006080860235055</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0006817654390230456</v>
+        <v>-0.001223988747828792</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01080378350489003</v>
+        <v>-0.0003808808645803625</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,25 +3623,25 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.01181310137317518</v>
+        <v>-0.009582392563433956</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0008381685397708642</v>
+        <v>0.004792282680358409</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.004862350778867071</v>
+        <v>0.02935028131923734</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3656,61 +3656,61 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.006843534023808278</v>
+        <v>-0.009032771127383293</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0157764611452142</v>
+        <v>0.002494260627664551</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.001861473262450153</v>
+        <v>0.01645145151754724</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.007205920475479606</v>
+        <v>-0.01864611896340648</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.003066894240017231</v>
+        <v>-0.01633763397191324</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.005713714626462293</v>
+        <v>0.003018915026514179</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.005063816843520678</v>
+        <v>-0.0008706939999725487</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
@@ -3719,10 +3719,10 @@
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.004475340972489872</v>
+        <v>-0.003552313689645682</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.02783408021321357</v>
+        <v>0.01671675020783294</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,28 +3731,28 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.001388061219344909</v>
+        <v>-0.01665666745191014</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.001984001330490174</v>
+        <v>-0.0116877500946867</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01043335171479595</v>
+        <v>0.01816061895633472</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
@@ -3764,19 +3764,19 @@
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01424351256497207</v>
+        <v>-0.01668180576237299</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01713909139120072</v>
+        <v>0.007471850227121493</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01391013615321212</v>
+        <v>-0.005097419912614723</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,25 +3785,25 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.00426125088272118</v>
+        <v>0.01067018564149998</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.002456629575707127</v>
+        <v>0.009854944762533428</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.003403540579331406</v>
+        <v>-0.01663939443415029</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,25 +3812,25 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01007688610767282</v>
+        <v>0.008086267213454151</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.005743995954093658</v>
+        <v>0.01355924230183663</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02700385267445353</v>
+        <v>0.01625671742875318</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.001117520143415066</v>
+        <v>-0.002545574142954273</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,13 +3868,13 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03899327710124503</v>
+        <v>0.01003540376433919</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02120388057548854</v>
+        <v>0.0500061065663549</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03335232726094153</v>
+        <v>-0.0112204998506439</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3895,49 +3895,49 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002934818048733</v>
+        <v>2.130567023878448e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.005969242663948245</v>
+        <v>0.000959652722603732</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.002906391586246278</v>
+        <v>-0.007812704012820386</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0001538045408506433</v>
+        <v>0.0001134338461926963</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04009894799020659</v>
+        <v>-0.02751195635198352</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02513378367856436</v>
+        <v>-0.01585699751574071</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01976965653953899</v>
+        <v>0.001733969946471408</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01995107355926626</v>
+        <v>0.01526562262412852</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01217992639081843</v>
+        <v>0.002349768216646225</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01076326427106674</v>
+        <v>-0.00470411174648369</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1919967109365086</v>
+        <v>0.1136540951651104</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1121078374175691</v>
+        <v>-0.0159406999351699</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,94 +4003,94 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.00532862564151352</v>
+        <v>0.01089564430748711</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.02465000361485901</v>
+        <v>-0.01015975687054489</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0416749440725773</v>
+        <v>-0.009982282736585399</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01194892502929363</v>
+        <v>0.005812871116137945</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.01141952307157808</v>
+        <v>0.001558409210624883</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08502288496115241</v>
+        <v>0.03412844439970378</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02335974946706425</v>
+        <v>0.005138514804890641</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.03008114223949967</v>
+        <v>0.0202878743084526</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.002873177571260898</v>
+        <v>-0.005761194107139475</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.00648979531718213</v>
+        <v>-0.00396591817962629</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.01896296629388057</v>
+        <v>-0.02427497008004944</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0003598519918068681</v>
+        <v>0.003282239556822708</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02538695371928449</v>
+        <v>0.01042322998735464</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.004151836511865153</v>
+        <v>-0.0205448940198044</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.01615805604335955</v>
+        <v>0.007612584187691116</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.006456267363711697</v>
+        <v>0.01546452012151337</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01993834812100076</v>
+        <v>-0.02459034620895778</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.007218463930577222</v>
+        <v>0.003545447053519209</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4165,22 +4165,22 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.01963704220114021</v>
+        <v>0.009972577307292556</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.06005919379025467</v>
+        <v>-0.01588260814731401</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04281788314127175</v>
+        <v>-0.004469671449062424</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4192,121 +4192,121 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0174463387640955</v>
+        <v>-0.006964614590987343</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001988562148309344</v>
+        <v>-0.006065632514319034</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.005160173793762352</v>
+        <v>0.0050571718473048</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.01638778587652838</v>
+        <v>-0.01157586160638462</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.01505873953301555</v>
+        <v>0.01291657952222289</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001471271227546094</v>
+        <v>-0.001534172551648922</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.005355514376816597</v>
+        <v>0.001538516333775991</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0003296546547079554</v>
+        <v>-0.02693232990762384</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0227937711017644</v>
+        <v>0.0002789488359972188</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.03147432494870072</v>
+        <v>0.00811412748536738</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.04856723356271492</v>
+        <v>-0.0114524934857886</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.002103418297344999</v>
+        <v>0.006095913784871609</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.02012518110622519</v>
+        <v>0.002978445300971584</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02831074443499862</v>
+        <v>-0.02936359985256203</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.004172389680217862</v>
+        <v>-0.001990288935015898</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01106488774082427</v>
+        <v>0.009814542970887656</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03620666625523155</v>
+        <v>-0.01396239249180516</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.004502677793020772</v>
+        <v>-0.003274877538145042</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,25 +4351,25 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.02007544905484211</v>
+        <v>0.0301454324638587</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.04813000779633519</v>
+        <v>0.007552572021144514</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.04074308335460378</v>
+        <v>-0.007901982459185303</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4378,19 +4378,19 @@
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.001465870187140767</v>
+        <v>-0.0005867573161498108</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.04770941555425202</v>
+        <v>-0.006813891805358803</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0223196070143871</v>
+        <v>0.0003547650306002431</v>
       </c>
     </row>
     <row r="8">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2418740112767277</v>
+        <v>0.07949174889937788</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1250375862257542</v>
+        <v>-0.08127961020611596</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03538497242143804</v>
+        <v>-0.01878333220999653</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5009,22 +5009,22 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2768487147592822</v>
+        <v>0.1294254723950857</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1906738518069495</v>
+        <v>-0.1828513051354793</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.08509029669213687</v>
+        <v>-0.04654674843507008</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5039,25 +5039,25 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.04117777378906302</v>
+        <v>0.01207243359163878</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.03360790526857772</v>
+        <v>-0.01326749542356726</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.06068728040665654</v>
+        <v>-0.02241602202352499</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,97 +5066,97 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1463138992804594</v>
+        <v>0.03117559536048393</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01378461789189075</v>
+        <v>-0.03834480968679173</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01147515994446391</v>
+        <v>-0.03777652540387466</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.07049952916264055</v>
+        <v>0.07906658062075778</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.05731339266715776</v>
+        <v>-0.06460389178856656</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.08998603437339664</v>
+        <v>0.03407272094880153</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.7206971569069524</v>
+        <v>0.2153012542162769</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.09999212430055791</v>
+        <v>-0.1296174902514882</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1259345521243715</v>
+        <v>-0.1738983578736577</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.007574082983889457</v>
+        <v>-0.004036044833790479</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.0707540871440579</v>
+        <v>-0.01911418585013245</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.163570927095918</v>
+        <v>0.002047341288001654</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.09593399169637268</v>
+        <v>0.003839894306462991</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1503416176353931</v>
+        <v>0.03884409991630225</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0935173000794213</v>
+        <v>0.0505851984805646</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,19 +5201,19 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.132306010681822</v>
+        <v>0.05892842064896014</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02794424041209777</v>
+        <v>0.03805420888893129</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02222877325494221</v>
+        <v>-0.01999099970845503</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,19 +5228,19 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1480856450670829</v>
+        <v>-0.09206458990571334</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.03265301500090308</v>
+        <v>0.1126263840980029</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02627367471326396</v>
+        <v>0.02229084465153022</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
         <v>-0</v>
@@ -5249,85 +5249,85 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.04094137933217858</v>
+        <v>-0.07315085170478119</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1151754728585549</v>
+        <v>0.160097313536703</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.08825616917526753</v>
+        <v>0.02713762103685794</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.122521576143167</v>
+        <v>-0.08883983269238263</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.074572551170572</v>
+        <v>0.1203823599706965</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.002045761350434659</v>
+        <v>0.03199958456836915</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.006097117400470229</v>
+        <v>-0.005495959519014648</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1233434094731598</v>
+        <v>0.03679608175121585</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.06466775568418233</v>
+        <v>-0.03356014911949508</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.09419627532957517</v>
+        <v>-0.09368976892981823</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.02971733794472444</v>
+        <v>0.0915015374838937</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.05847730898515863</v>
+        <v>-0.01926879747531425</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -5360,28 +5360,28 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.04454068649766235</v>
+        <v>-0.009026238444501818</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.005765853906322373</v>
+        <v>0.08020401091488993</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.02734969185475737</v>
+        <v>-0.01297999133547905</v>
       </c>
       <c r="EB9" t="n">
         <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,16 +5390,16 @@
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.05766249283168939</v>
+        <v>-0.03664931435019248</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.02484903597407933</v>
+        <v>0.07879051886591854</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04004548862102</v>
+        <v>0.0409426303890519</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
@@ -5408,31 +5408,31 @@
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1197420390427088</v>
+        <v>-0.08740246600804416</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.08341454365550838</v>
+        <v>-0.08846882755083355</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.06727122994108466</v>
+        <v>0.04961524921824777</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,76 +5444,76 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1239776212068866</v>
+        <v>-0.1046306814979082</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.06232412900230565</v>
+        <v>0.1355914455735764</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.01621126264659254</v>
+        <v>0.02483157171764746</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.07547027528232073</v>
+        <v>-0.04588157189111412</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.06672775893857767</v>
+        <v>-0.01326047441583847</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.1164298650897057</v>
+        <v>-0.007234643367893479</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.003580409906300329</v>
+        <v>0.07689561660639538</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.04310999441749257</v>
+        <v>0.1562030442117985</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.06918640607778154</v>
+        <v>-0.06927878217421825</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5522,16 +5522,16 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.018025212765149</v>
+        <v>-0.03572495440791948</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02549680719467034</v>
+        <v>0.03535679102565641</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5543,10 +5543,10 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6680495974710107</v>
+        <v>0.1434888394034776</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1776545725219413</v>
+        <v>-0.09235791336028425</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.09288211984650331</v>
+        <v>-0.02846408734815935</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0385904520171348</v>
+        <v>0.03655724393067789</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,52 +5581,52 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3786005791292386</v>
+        <v>0.09477605041816087</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2592969215094497</v>
+        <v>-0.2514740025343434</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.151104871812844</v>
+        <v>-0.08829637491922394</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.02772051511276779</v>
+        <v>0.01855642132689463</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04844816170348981</v>
+        <v>0.0030713000407457</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1015601465031998</v>
+        <v>-0.09720549546153701</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1441182365062264</v>
+        <v>-0.1239470342480903</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01296115050783215</v>
+        <v>0.03970203954864756</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,16 +5635,16 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1755727538274607</v>
+        <v>0.03433980025565909</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08631126763373584</v>
+        <v>-0.0118157452544302</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.03854446554707245</v>
+        <v>-0.1860533484362418</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.05295433411061456</v>
+        <v>0.005030114582455681</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -5662,16 +5662,16 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.04576420899439739</v>
+        <v>0.106017242270877</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.08278887572114285</v>
+        <v>-0.06160494835870618</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.0874623466611345</v>
+        <v>0.03070197308340298</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.009326705715454549</v>
+        <v>-0.03311690961986694</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,43 +5689,43 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4427764531552204</v>
+        <v>0.2012755929284643</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.06216490533427546</v>
+        <v>-0.07886340171067389</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.08713971397364777</v>
+        <v>-0.2741083952166092</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.1140906198964016</v>
+        <v>-0.1343649903500319</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.06892022170666215</v>
+        <v>-0.08566394203289893</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.06413893003216034</v>
+        <v>-0.008303429628338041</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2641457971079297</v>
+        <v>-0.07426547123114143</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,61 +5734,61 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.02304867683462804</v>
+        <v>0.03178287401507597</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1350959714438908</v>
+        <v>0.05067656386823374</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.29322182356085</v>
+        <v>0.06972809071136099</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.07128849975319437</v>
+        <v>0.04997796854239259</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.02021189607236218</v>
+        <v>0.00889573209792221</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2593626954629049</v>
+        <v>0.1372891852380783</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.05325318854658392</v>
+        <v>-0.09129414185828963</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.08626888410673833</v>
+        <v>-0.07978933564092495</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0.01306345010143796</v>
+        <v>-0.04517251393017298</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5797,70 +5797,70 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.2028890567041946</v>
+        <v>-0.07116004497406353</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.06185224576813347</v>
+        <v>0.095894088624796</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.04783275573467429</v>
+        <v>0.02741273696159688</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.02190920491718519</v>
+        <v>-0.01134044100512568</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.1784455504373447</v>
+        <v>-0.1021768863350389</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.08143880125671039</v>
+        <v>0.1006814383695555</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.01369247944995985</v>
+        <v>0.1866764527469882</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.08962043758154811</v>
+        <v>0.09251059692341057</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1675737140107139</v>
+        <v>-0.07375820975332144</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.1310855818490913</v>
+        <v>0.1114508992460548</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.04807833026413967</v>
+        <v>0.04306923616523788</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,88 +5869,88 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.01348110564569827</v>
+        <v>-0.02147081025077498</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.2002606477785859</v>
+        <v>-0.009211921805688923</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.1266478250851493</v>
+        <v>0.02221848073952075</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05278723526135945</v>
+        <v>-0.02074405313342954</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.005748591268894891</v>
+        <v>-0.03419540501989727</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1603836071402916</v>
+        <v>-0.04015283375275731</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.09351039722562554</v>
+        <v>0.01750085293786547</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.01625501187125037</v>
+        <v>-0.1336216084740705</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.05995387052268462</v>
+        <v>0.125174261870906</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.00273531877126306</v>
+        <v>0.04648900218422056</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.05909662198250263</v>
+        <v>0.1138310940647252</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.1147652277876259</v>
+        <v>-0.08687042974507689</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.04366507412783749</v>
+        <v>0.2040439208260673</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
@@ -5959,52 +5959,52 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.05725724312842326</v>
+        <v>-0.02627231927989276</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.007864481337770847</v>
+        <v>0.07727524837691178</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04935196896970138</v>
+        <v>-0.02639236731322368</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.1124819657696992</v>
+        <v>0.00132068045889859</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1914158163682769</v>
+        <v>-0.02364597741745277</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.122609780387416</v>
+        <v>0.1112619934660875</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.07501979012232891</v>
+        <v>0.06901226023868699</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.09449856261217283</v>
+        <v>0.007990711058658563</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
@@ -6013,106 +6013,106 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1843865684204173</v>
+        <v>-0.09737281365343546</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.1298816116981927</v>
+        <v>0.1184156234291129</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.01251745737396787</v>
+        <v>0.0372535497024234</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.01670634996445259</v>
+        <v>-0.01385279322187559</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.02107439719227763</v>
+        <v>-0.04173107002467563</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.1070778471456359</v>
+        <v>0.01919730275510094</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.1196855865355499</v>
+        <v>0.09562652136110975</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.04229551739352066</v>
+        <v>0.005045106200713654</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.1165721546009291</v>
+        <v>0.0965002300525928</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.1331927491390575</v>
+        <v>0.1864040325908811</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.131372216842537</v>
+        <v>-0.1103428204253908</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.1105990811717794</v>
+        <v>0.0225438868066834</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.0687191065814473</v>
+        <v>-0.036041198436554</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03243028290414427</v>
+        <v>0.01780118541235614</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.1332422695045047</v>
+        <v>-0.006175759221281605</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03511264425716158</v>
+        <v>0.2828735974316861</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,16 +6132,16 @@
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04786620523357611</v>
+        <v>0.06504670740754057</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05358377715243218</v>
+        <v>-0.2420972318133699</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01045814454850284</v>
+        <v>0.2350207273012726</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,13 +6159,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.04618232362663947</v>
+        <v>0.008409181915440052</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.03324246744902266</v>
+        <v>-0.1667230466924831</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-0</v>
@@ -6174,10 +6174,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.001841127431918004</v>
+        <v>0.03113023274772018</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,52 +6186,52 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.005741567332580702</v>
+        <v>-0.05146990257470412</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00584746507276106</v>
+        <v>-0.01102918795292943</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03728490889969966</v>
+        <v>-0.02314607660610439</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03052883448216068</v>
+        <v>-0.1699209655363943</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01513970959843522</v>
+        <v>0.09534414467703693</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.008481410524637198</v>
+        <v>0.05876178602952422</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,25 +6240,25 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02756801624397509</v>
+        <v>-0.007731129115978551</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.007968902963174252</v>
+        <v>-0.01791273531332607</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.05093939618284897</v>
+        <v>0.2108319983295628</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,79 +6267,79 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.03459209094946074</v>
+        <v>-0.07235625037124062</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.001321096230362836</v>
+        <v>-0.02413201217654796</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.008722444363639149</v>
+        <v>0.06409128014034739</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.04252905267083037</v>
+        <v>-0.02700104660718328</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.06592625455770286</v>
+        <v>-0.1571485961482459</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.06820957651922373</v>
+        <v>0.04301971401325416</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.03256449634738866</v>
+        <v>0.126797099194728</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.02511498431650253</v>
+        <v>0.08815584922847644</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.01244585650693464</v>
+        <v>0.1417856825646552</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.02301584613549622</v>
+        <v>0.006071880701127224</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.009576303069132659</v>
+        <v>-0.08106551439819551</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6360,94 +6360,94 @@
         <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.001565788669519387</v>
+        <v>-0.1243076166204449</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01317867033879492</v>
+        <v>-0.04428010193347354</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02292325436810761</v>
+        <v>0.1144350820921029</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.006222975773841479</v>
+        <v>-0.1123837459746801</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.02164493736912848</v>
+        <v>0.04826190678958275</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.007963391377054192</v>
+        <v>0.04822191592906902</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.01256974604228599</v>
+        <v>-0.1094593920285892</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>-0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01414977543031494</v>
+        <v>-0.03553999080626662</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01720293712445705</v>
+        <v>0.1198228824173188</v>
       </c>
       <c r="DB11" t="n">
         <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.01165333498534188</v>
+        <v>-0.1037544638173798</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,40 +6456,40 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.0008243141024796614</v>
+        <v>-0.1251816841691205</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01709361550347861</v>
+        <v>0.07863866854866765</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.004043946826455641</v>
+        <v>-0.05640923313772568</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0177350240073086</v>
+        <v>-0.03370905726442141</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.01151790992270717</v>
+        <v>0.003064435480684225</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
@@ -6501,22 +6501,22 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.008532028906276362</v>
+        <v>-0.02511369898198837</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.03109577371394135</v>
+        <v>0.0410278415085709</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.007500538114993744</v>
+        <v>0.04164102621912932</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
@@ -6528,34 +6528,34 @@
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.007864842094688251</v>
+        <v>-0.0682917479707221</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.005293227663094626</v>
+        <v>-0.06457023362787392</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.004838754017052708</v>
+        <v>0.07392628543755368</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0001135004027913972</v>
+        <v>-0.05869885736341435</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
@@ -6564,16 +6564,16 @@
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.008214505737009386</v>
+        <v>-0.1030817051586412</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.02022178276018564</v>
+        <v>0.1111206919725197</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
@@ -6582,34 +6582,34 @@
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.007692565545412188</v>
+        <v>-0.1277805227575195</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01762810031360725</v>
+        <v>-0.07202393715352146</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02017095550314064</v>
+        <v>0.09534129999367828</v>
       </c>
       <c r="FD11" t="n">
         <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.003996990988225545</v>
+        <v>-0.1610439620582372</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
@@ -6618,16 +6618,16 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03799571533791996</v>
+        <v>0.06721093146955012</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02205916234910756</v>
+        <v>0.1237378248648924</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01007585407916934</v>
+        <v>0.07020549367494941</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,28 +6645,28 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.02145317129325435</v>
+        <v>0.07331879812719815</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.03811836849433511</v>
+        <v>0.03552648325057545</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.038910107545609</v>
+        <v>-0.05954836175610929</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
@@ -6675,13 +6675,13 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.02569092692086979</v>
+        <v>0.1170459497742514</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4971616594229025</v>
+        <v>0.3869235204020666</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3339513535814245</v>
+        <v>-0.2870438411340536</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08697319193417523</v>
+        <v>-0.001485456079741016</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6716,25 +6716,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2583784507027506</v>
+        <v>0.3129894923493378</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3168287106172496</v>
+        <v>-0.3355025232731088</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1058801880003946</v>
+        <v>-0.0275996828337897</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6743,28 +6743,28 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06990674997068698</v>
+        <v>0.05095932793919723</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01832909120386674</v>
+        <v>-0.02704658713502648</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.07641214150940683</v>
+        <v>-0.04373623441053008</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,43 +6773,43 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.179013736234534</v>
+        <v>-0.06952648677307592</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.1216735003702634</v>
+        <v>-0.07243648617672535</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.07750960116374031</v>
+        <v>-0.003358350393887753</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.05308347986018055</v>
+        <v>0.1129716544600727</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04738832910597529</v>
+        <v>-0.0768200831360573</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.08558072325308295</v>
+        <v>0.0710162032378506</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,25 +6818,25 @@
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3814777933808819</v>
+        <v>0.2144642559953516</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.1023660556618522</v>
+        <v>-0.2245991248642644</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.03652821312482558</v>
+        <v>-0.08413326632076565</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6848,22 +6848,22 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01669531596254447</v>
+        <v>0.0005110421240606858</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.1134796187868132</v>
+        <v>-0.01809275114054603</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1925348419053894</v>
+        <v>-0.01003760762434087</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6881,49 +6881,49 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.09266550812314144</v>
+        <v>-0.09163280523151378</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.09606888507038379</v>
+        <v>0.02562205351454683</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01541494111939477</v>
+        <v>0.001756166405656301</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2006980987011695</v>
+        <v>0.1901790362526852</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.05157820749284373</v>
+        <v>-0.08682611906078098</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.0524643897461034</v>
+        <v>-0.001456437294144877</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
@@ -6935,46 +6935,46 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1311655484750846</v>
+        <v>-0.1812479605422979</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01745824298078072</v>
+        <v>0.1856272328254405</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.02592869095072965</v>
+        <v>-0.02184871516659864</v>
       </c>
       <c r="CI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.03394500656426674</v>
+        <v>-0.1352105588874186</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1437012544145646</v>
+        <v>0.2607896608581372</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.08240962692248453</v>
+        <v>0.008811833443742275</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,52 +6983,52 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.09719377689288963</v>
+        <v>-0.1768901421896259</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.05769371303376307</v>
+        <v>0.1816434181732645</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01694675509004162</v>
+        <v>-0.003691598034578133</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.0890546879899877</v>
+        <v>-0.09897344662081101</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03990682973829843</v>
+        <v>0.03076586044622783</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1108818835566106</v>
+        <v>-0.07501217159258844</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7043,22 +7043,22 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.1434955730286506</v>
+        <v>-0.09557462863003857</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.1258773169091371</v>
+        <v>0.09582903121749213</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.06290207911081828</v>
+        <v>-0.007492078335102573</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
@@ -7070,25 +7070,25 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.0145394966966368</v>
+        <v>0.004209288672940424</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.153424668885085</v>
+        <v>-0.1120198944295314</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.1167047957573919</v>
+        <v>0.08055600236025144</v>
       </c>
       <c r="EB12" t="n">
         <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
@@ -7097,97 +7097,97 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.007851777800071723</v>
+        <v>-0.130092611907531</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.04373455475429987</v>
+        <v>0.1460617842940079</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.06769593345315608</v>
+        <v>0.05040688741843316</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.09175406953360153</v>
+        <v>-0.1637602045069184</v>
       </c>
       <c r="EQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.1352076913075004</v>
+        <v>0.1186512418553561</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.05324426561575844</v>
+        <v>0.02562071864234316</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.09493309532592072</v>
+        <v>-0.1888396376525835</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.06032891768779875</v>
+        <v>0.2100812052004616</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.02256212107276974</v>
+        <v>-0.02345833460085715</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.013457596677816</v>
+        <v>-0.09736549432176755</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.06475023582785218</v>
+        <v>0.06229743796384015</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.05212836808547901</v>
+        <v>-0.04448524833849297</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
@@ -7196,49 +7196,49 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.09154569794089573</v>
+        <v>0.1505681711098697</v>
       </c>
       <c r="FR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.004667863345909163</v>
+        <v>0.2056299332223234</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.1635136838435108</v>
+        <v>0.1093050387539268</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.01460299198397233</v>
+        <v>-0.1250641321253103</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.02173869408645528</v>
+        <v>0.1285046603042025</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
@@ -7250,18 +7250,18 @@
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1005911650949834</v>
+        <v>0.3693493755110977</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01084080098310235</v>
+        <v>0.02484910558115799</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1557294700812668</v>
+        <v>-0.3398508501041428</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06148527404883617</v>
+        <v>0.342177099647989</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,13 +7297,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01011328979991649</v>
+        <v>-0.07992995637532159</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1208123215782427</v>
+        <v>-0.2474562017923542</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-0</v>
@@ -7312,10 +7312,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.00053769401251177</v>
+        <v>0.04742848723946759</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,37 +7324,37 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.02302713237053389</v>
+        <v>-0.09314058656361521</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01405136092641092</v>
+        <v>-0.04610134707199225</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.03265983987935099</v>
+        <v>-0.06583861270449064</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.04428703272861766</v>
+        <v>-0.2250764498014677</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.0133990690503663</v>
+        <v>-0.1068695539144389</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.007223073913532604</v>
+        <v>0.1096882263226317</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.005705284140946243</v>
+        <v>0.03667118260203676</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.01258891072336658</v>
+        <v>-0.08669999868146396</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7396,19 +7396,19 @@
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.06894555312197659</v>
+        <v>0.3493049673818111</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01138019346905625</v>
+        <v>-0.1223601626185133</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.04655703364081429</v>
+        <v>-0.09006367770802175</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -7420,10 +7420,10 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03339336156809965</v>
+        <v>-0.02933030355526779</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.03455620416058953</v>
+        <v>-0.1339742612826019</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.06883925298825823</v>
+        <v>-0.2785858159149457</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
         <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.03820524384816013</v>
+        <v>-0.02294729095045347</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,13 +7459,13 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0368998571578816</v>
+        <v>0.06979958254022084</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0.002042135948463064</v>
+        <v>0.06775193406439656</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.02457011790871964</v>
+        <v>0.1826125023131324</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,16 +7486,16 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.006799680280820995</v>
+        <v>-0.08390696279457535</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.04373077059390808</v>
+        <v>-0.1822519401889715</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
@@ -7504,22 +7504,22 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.01943124924627119</v>
+        <v>-0.1592886624055519</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.001344701322730653</v>
+        <v>-0.005911194539289022</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.04165363983945763</v>
+        <v>0.1797376600870118</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,19 +7531,19 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.0008035395603495936</v>
+        <v>-0.2250856087100169</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.02842453149835789</v>
+        <v>0.3453728680394499</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.008798530314759393</v>
+        <v>0.3505433956219024</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,25 +7552,25 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.009582962846596836</v>
+        <v>-0.14306362252735</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.003175841010754278</v>
+        <v>0.003054843811904947</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.033371322626078</v>
+        <v>0.1640547078414992</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7585,25 +7585,25 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.002485920368895366</v>
+        <v>-0.07634396934378376</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02415173636842456</v>
+        <v>-0.1220884147370848</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.03846069994383697</v>
+        <v>0.04766542044985802</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
@@ -7612,61 +7612,61 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.01438793540723831</v>
+        <v>-0.02709922576069465</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03341453597548136</v>
+        <v>0.03803692939554901</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.03817875315523119</v>
+        <v>0.1065039839191348</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01298100565959176</v>
+        <v>0.01325580661799749</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.006062075733515255</v>
+        <v>0.0937820634874242</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.03797352920778356</v>
+        <v>0.1691647820569635</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.01795091429751516</v>
+        <v>-0.11103445887203</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,10 +7675,10 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.003881656480142393</v>
+        <v>-0.02873396069488439</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.004051076388172398</v>
+        <v>0.04802133509304733</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7687,13 +7687,13 @@
         <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01717478674339706</v>
+        <v>-0.07033538264001682</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,37 +7702,37 @@
         <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.03261046755850285</v>
+        <v>-0.02185881510351351</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.05067514387884052</v>
+        <v>0.1255655935642554</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.01254508200608343</v>
+        <v>-0.1655858722757115</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.003221578291098326</v>
+        <v>-0.02825937111882039</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03339487553337511</v>
+        <v>0.1534976788122933</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
@@ -7741,28 +7741,28 @@
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.02823544032334769</v>
+        <v>-0.202760612055226</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.007473652363467034</v>
+        <v>0.04627261980648197</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.03317028864167206</v>
+        <v>-0.0407654620843616</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
         <v>0</v>
@@ -7771,22 +7771,22 @@
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.001581726517950634</v>
+        <v>0.07697802866798685</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0379659729026988</v>
+        <v>0.2570278121684756</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01162864627808914</v>
+        <v>-0.02141416448797334</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,31 +7795,31 @@
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02071322943641828</v>
+        <v>-0.0646840876689156</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01256486136583515</v>
+        <v>0.1024943894163204</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7830,16 +7830,16 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7433451010109444</v>
+        <v>0.2809203612781949</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3770224649593173</v>
+        <v>-0.1605354946910153</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1001116695650554</v>
+        <v>-0.01526203393595856</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7851,28 +7851,28 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3820873666756013</v>
+        <v>0.2055494058222923</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.298263780616028</v>
+        <v>-0.182442099152396</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.09565064751895566</v>
+        <v>-0.03264094268944738</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -7881,22 +7881,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1242806419446756</v>
+        <v>0.0131801249353618</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.06139328584194257</v>
+        <v>-0.01487099580602589</v>
       </c>
       <c r="W14" t="n">
-        <v>0.009836577863507544</v>
+        <v>-0.02094193695249294</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
@@ -7908,19 +7908,19 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.07810115765964468</v>
+        <v>-0.04266399521269348</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.04267280322441529</v>
+        <v>-0.1658950208816785</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.01876786571367825</v>
+        <v>-0.0704054669547395</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
@@ -7929,88 +7929,88 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.006999890731607882</v>
+        <v>0.09535161745848356</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.0764272757443023</v>
+        <v>-0.04637434264004404</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.07531388881946316</v>
+        <v>0.06536173891376339</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.5854539478069409</v>
+        <v>0.2199761404748735</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.01586588620060359</v>
+        <v>-0.001925795198206734</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.07576965409750344</v>
+        <v>-0.03220959302543197</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0992286545795123</v>
+        <v>0.02822587998792595</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.1919862409296147</v>
+        <v>-0.05959184907975223</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.2520674731022088</v>
+        <v>-0.03049632159887894</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -8019,22 +8019,22 @@
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.168826672222465</v>
+        <v>0.01170933180466149</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.03609262055554014</v>
+        <v>0.0183362455094774</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.2195369251210382</v>
+        <v>0.1294381823352017</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8046,46 +8046,46 @@
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.2908538676010433</v>
+        <v>0.2193326063195695</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.01983422371252486</v>
+        <v>-0.03855994598352904</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.03868422775952693</v>
+        <v>0.02479562908968182</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.1587465647657897</v>
+        <v>-0.09079680108943827</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.05329041687965474</v>
+        <v>0.08506390324992949</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.03995698603927551</v>
+        <v>0.01559023219217015</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
         <v>-0</v>
@@ -8094,52 +8094,52 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.003770520618682016</v>
+        <v>-0.1363576368115486</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1463984238023994</v>
+        <v>0.1520971251753419</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.133581181514511</v>
+        <v>-0.02612765184716891</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.1419056579009835</v>
+        <v>-0.08095406507767686</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.08213313900944659</v>
+        <v>0.07695078865063645</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.02429028399428066</v>
+        <v>0.02328297156561651</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8148,112 +8148,112 @@
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.009673012770790114</v>
+        <v>0.001574317696125671</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.06806898787657917</v>
+        <v>-0.01517133532098399</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.0007826332872442186</v>
+        <v>-0.03623802066627514</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.08370053392485885</v>
+        <v>-0.1433022085420892</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.02594599109960679</v>
+        <v>-0.02867590990272211</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.03360930030672184</v>
+        <v>0.08029485317231955</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.06320862041250111</v>
+        <v>0.05561865247836002</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.01857106313420376</v>
+        <v>0.04865777142193304</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.03133328931585917</v>
+        <v>-0.07850259349744194</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.1432181570415455</v>
+        <v>-0.02827467337685136</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.07178426522784101</v>
+        <v>0.07268672048923694</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.07386151636220031</v>
+        <v>0.07479074753033671</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,43 +8262,43 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.1089295061894343</v>
+        <v>-0.05225630757687885</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.06621111334792458</v>
+        <v>0.08609714500528622</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.007793626932567636</v>
+        <v>-0.01369704676428313</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.1469093456906204</v>
+        <v>-0.09184870478583823</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.05930977180510168</v>
+        <v>0.09079514135321864</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0007189905322051289</v>
+        <v>0.001278700175683257</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
@@ -8310,58 +8310,58 @@
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.0008107590424787577</v>
+        <v>0.0147942925204231</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.05100874570502125</v>
+        <v>-0.003812830919927459</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.05350412346663815</v>
+        <v>-0.147032683909346</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.01070682270441215</v>
+        <v>0.000821698749838017</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.04635151669329013</v>
+        <v>0.05345822785846959</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.02010131094043821</v>
+        <v>-0.02658620988503387</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
@@ -8370,19 +8370,19 @@
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.02689553413508184</v>
+        <v>-0.07179713362936227</v>
       </c>
       <c r="GA14" t="n">
         <v>-0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.06330544011969864</v>
+        <v>0.03916881202954367</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
@@ -8399,25 +8399,25 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.5419160421013971</v>
+        <v>-0.5094673135064166</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.24281995906891</v>
+        <v>0.2951431887529217</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1175890119395225</v>
+        <v>0.1143273431182506</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
@@ -8426,46 +8426,46 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3096199073956373</v>
+        <v>-0.3562134810328955</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.245739319360539</v>
+        <v>0.3470325707498867</v>
       </c>
       <c r="N15" t="n">
-        <v>0.04998088698848774</v>
+        <v>0.0984501852707847</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1610180080454925</v>
+        <v>-0.07898098169696345</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02187366684797475</v>
+        <v>0.06084798357664056</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.04230697704284708</v>
+        <v>-0.03288626475045162</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -8477,55 +8477,55 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.2069242297646917</v>
+        <v>-0.02368939338427294</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.04927938791977696</v>
+        <v>0.2001567081955108</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02433979964709401</v>
+        <v>-0.07912635920850596</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.05596935076415895</v>
+        <v>-0.1857117954311091</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.02268652772469194</v>
+        <v>0.06737864019054522</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.02242913184635648</v>
+        <v>-0.2418978937402323</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
@@ -8534,43 +8534,43 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.3512701613187955</v>
+        <v>-0.5284267654234618</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.04294099318354688</v>
+        <v>0.2017051908178228</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.00773428081732945</v>
+        <v>-0.03084367158506028</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
         <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.07524732481990852</v>
+        <v>0.07618000995405343</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.1165044077369513</v>
+        <v>0.02142087823488628</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.2995610014274832</v>
+        <v>0.204388324957858</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
@@ -8579,7 +8579,7 @@
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>-0</v>
@@ -8588,43 +8588,43 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.04351376335264334</v>
+        <v>0.1119314742714808</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.04380693376717204</v>
+        <v>0.01443689759573216</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1008676010419215</v>
+        <v>0.06479187813924762</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.268341565981168</v>
+        <v>-0.3965004444778182</v>
       </c>
       <c r="BW15" t="n">
         <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0952057469673329</v>
+        <v>0.1419763963876182</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.03772189852605794</v>
+        <v>-0.04323405072322261</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
@@ -8642,46 +8642,46 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1195416147029042</v>
+        <v>0.2597263916366193</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.04522609976159039</v>
+        <v>-0.08862138410514356</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.06021203092655837</v>
+        <v>-0.01643620297727688</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.06980233065185577</v>
+        <v>0.3090978278004816</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.004483248002048729</v>
+        <v>-0.1102864473122162</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0231057140719887</v>
+        <v>-0.1949956709922355</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
@@ -8696,49 +8696,49 @@
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.1302780847319421</v>
+        <v>0.2628959930338178</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.06064867530140635</v>
+        <v>-0.110745814760378</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0418884445377744</v>
+        <v>-0.02309538997126956</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD15" t="n">
         <v>-0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1304472618486436</v>
+        <v>0.04066990264139227</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.03892300800583744</v>
+        <v>-0.01100007069050543</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.001727896846971471</v>
+        <v>-0.000283134293474081</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
@@ -8747,19 +8747,19 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.1300946910390542</v>
+        <v>0.1249857362208682</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.0857418153291431</v>
+        <v>-0.03578750730200107</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.158253041289425</v>
+        <v>0.02370401897130172</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8768,28 +8768,28 @@
         <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.0645658223283984</v>
+        <v>-0.03160833415972017</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.1763157900323623</v>
+        <v>0.01244334003308044</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.09719532685592762</v>
+        <v>-0.01518987848882384</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8804,25 +8804,25 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.05864898369874328</v>
+        <v>0.2718934072522684</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.02956522888730608</v>
+        <v>-0.0688111336098968</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.06864093887513066</v>
+        <v>-0.04179423483157284</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
@@ -8831,162 +8831,162 @@
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0718871259848176</v>
+        <v>0.1693139915511016</v>
       </c>
       <c r="EQ15" t="n">
         <v>0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.06954216334917364</v>
+        <v>-0.09233037503688638</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.07556231985991384</v>
+        <v>-0.1025670031360575</v>
       </c>
       <c r="ET15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
         <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.14541140053422</v>
+        <v>0.3039283381769178</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.07568012548920496</v>
+        <v>-0.1003105117901835</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03673872678562203</v>
+        <v>-0.02061150146322889</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.03690545472273516</v>
+        <v>0.1530268483386518</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.03620481897631962</v>
+        <v>-0.09262537529231604</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.013592908904402</v>
+        <v>0.08182283942266112</v>
       </c>
       <c r="FL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM15" t="n">
         <v>-0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.02061486742525605</v>
+        <v>0.02883211382574551</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.1783832090515866</v>
+        <v>-0.06846372670478533</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.03393670637389745</v>
+        <v>-0.003923152316712886</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.07024463892800595</v>
+        <v>0.1832553007356105</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.1299703148270701</v>
+        <v>-0.04057946854669352</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3340438755300984</v>
+        <v>0.2044259832215142</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.09416441235929329</v>
+        <v>-0.1499949195892503</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08111904231008162</v>
+        <v>0.1484738356381059</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8998,22 +8998,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2439510602214868</v>
+        <v>0.1816371309260741</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.09781014033832346</v>
+        <v>-0.1526096011519296</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1240392483071559</v>
+        <v>0.09082758766406233</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9025,19 +9025,19 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09713897809282546</v>
+        <v>0.04132341135331856</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.03022541789480143</v>
+        <v>-0.04202783274744683</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03176677749928347</v>
+        <v>-0.02119248831408843</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>-0</v>
@@ -9049,16 +9049,16 @@
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.06360513665548304</v>
+        <v>0.04793906252760022</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.04558846543739795</v>
+        <v>0.09431720592918656</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03628686871525748</v>
+        <v>0.0404507435358564</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -9067,7 +9067,7 @@
         <v>-0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -9079,49 +9079,49 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.01393048296128684</v>
+        <v>0.04898644454024619</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.03360813812514041</v>
+        <v>-0.03189092672781117</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.0666349040389084</v>
+        <v>0.007675756884389018</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.1655788476775633</v>
+        <v>0.204548887728163</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.01560045412525943</v>
+        <v>-0.2180521754076369</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1642227990489524</v>
+        <v>0.01398593650154294</v>
       </c>
       <c r="AY16" t="n">
         <v>-0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,16 +9130,16 @@
         <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.08415802079344267</v>
+        <v>-0.01027431528423423</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.02065491138110848</v>
+        <v>0.1268658770791365</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.08397722680833761</v>
+        <v>0.06754526825679824</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -9154,49 +9154,49 @@
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.03824546883659527</v>
+        <v>-0.07292660958878534</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.05864867197975188</v>
+        <v>-0.1033937367677041</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1319784780534426</v>
+        <v>-0.1619231782428798</v>
       </c>
       <c r="BQ16" t="n">
         <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.06562010493383454</v>
+        <v>0.115252496275339</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0.02637017692956205</v>
+        <v>-0.1267793006879149</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.09752204316394178</v>
+        <v>-0.01882849556294201</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA16" t="n">
         <v>0</v>
@@ -9205,28 +9205,28 @@
         <v>-0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE16" t="n">
         <v>-0</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0.07244843748921474</v>
+        <v>-0.084090576429613</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.02329392070746626</v>
+        <v>0.06870667129741444</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.004758822241223395</v>
+        <v>-0.03574906861520454</v>
       </c>
       <c r="CI16" t="n">
         <v>0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9235,55 +9235,55 @@
         <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.01749784617661943</v>
+        <v>-0.007424025835794197</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.01983367966106321</v>
+        <v>0.1555903900229161</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.124424635823879</v>
+        <v>0.009055860972084426</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS16" t="n">
         <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
         <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0.0556852036998321</v>
+        <v>-0.06065283368969369</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.02373085443441363</v>
+        <v>0.06975408393842528</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.02886582948563264</v>
+        <v>-0.05333585445230395</v>
       </c>
       <c r="DA16" t="n">
         <v>-0</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
         <v>0</v>
@@ -9292,16 +9292,16 @@
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0.03595593492190684</v>
+        <v>-0.01377954231434291</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.03963889953411061</v>
+        <v>0.02614027214942493</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.002940690298625722</v>
+        <v>-0.02090644240544691</v>
       </c>
       <c r="DJ16" t="n">
         <v>0</v>
@@ -9313,22 +9313,22 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
         <v>-0</v>
       </c>
       <c r="DP16" t="n">
-        <v>-0.003922390200513025</v>
+        <v>-0.01951380227929182</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.02451794197222971</v>
+        <v>0.06329141705962626</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.1321886685058069</v>
+        <v>-0.07282662289153478</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -9337,7 +9337,7 @@
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,16 +9346,16 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.06371467190210452</v>
+        <v>0.02678921764638336</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.003426352596941492</v>
+        <v>0.04613240012478258</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.06852304782435122</v>
+        <v>0.09522376747518538</v>
       </c>
       <c r="EB16" t="n">
         <v>0</v>
@@ -9370,46 +9370,46 @@
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0.1119081560373049</v>
+        <v>-0.04468971498383655</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.04692045356474604</v>
+        <v>0.05095673586784902</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.0602954127677601</v>
+        <v>0.0216778793735885</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
         <v>0</v>
       </c>
       <c r="EQ16" t="n">
-        <v>-0.007098793659395275</v>
+        <v>-0.0531158761711108</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.02726167522552808</v>
+        <v>0.07199894251963973</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02401818202475038</v>
+        <v>0.0150964887773984</v>
       </c>
       <c r="ET16" t="n">
         <v>0</v>
@@ -9418,103 +9418,103 @@
         <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ16" t="n">
-        <v>-0.06942897416451115</v>
+        <v>-0.06762701162714008</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.03771866476456184</v>
+        <v>0.1014196266391742</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.02821617680824693</v>
+        <v>-0.04026009452565392</v>
       </c>
       <c r="FC16" t="n">
         <v>0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0.00704193741859249</v>
+        <v>-0.01823134940945335</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.008856894008899628</v>
+        <v>0.07190572377164137</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.07422186497351735</v>
+        <v>0.002997041511051565</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0.006097050541471913</v>
+        <v>0.0007384754090509363</v>
       </c>
       <c r="FS16" t="n">
-        <v>-0.006314526016534962</v>
+        <v>-0.006289059486497676</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.07116569187210106</v>
+        <v>0.1726796836335774</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.04932868410382176</v>
+        <v>-0.03030387590176661</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.04668623404967054</v>
+        <v>0.1389079032088039</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
@@ -9537,19 +9537,19 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1826481596684845</v>
+        <v>0.4060691068627891</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.08032578134935006</v>
+        <v>-0.02354618662433754</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06736872531833712</v>
+        <v>-0.2341676763374637</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
@@ -9564,61 +9564,61 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1116275671928374</v>
+        <v>0.488532653872989</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.04754352768779612</v>
+        <v>-0.1397170476705887</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.03457818057300548</v>
+        <v>-0.126548728405686</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01933184771205974</v>
+        <v>0.06108434186059048</v>
       </c>
       <c r="U17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.03079747761225275</v>
+        <v>-0.07547235993875218</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02889448121022397</v>
+        <v>0.008349281638255813</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB17" t="n">
         <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.03720111347725556</v>
+        <v>0.01338584297490699</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -9627,40 +9627,40 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.02555565233532337</v>
+        <v>-0.1956713072279525</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.002689175338362269</v>
+        <v>-0.04696680353165718</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.02947520652860531</v>
+        <v>0.08243517316374542</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01886626861178974</v>
+        <v>-0.0321531167467636</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.02868882975935926</v>
+        <v>-0.06345699158775629</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,91 +9669,91 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1196566491650138</v>
+        <v>0.4558884813734828</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.06333870851599262</v>
+        <v>-0.1949748227808658</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.0525529343728259</v>
+        <v>-0.1633479582898902</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04133276380410803</v>
+        <v>0.03135632995225288</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.03363049694627965</v>
+        <v>-0.06742540389005079</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.007320072729079695</v>
+        <v>-0.07415358889139563</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.05425161671165871</v>
+        <v>0.07056729676785159</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.03093411696230106</v>
+        <v>0.09434114484018057</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.02106941754549382</v>
+        <v>0.05568389754945543</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.07167540801944061</v>
+        <v>0.2707416768468819</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,16 +9762,16 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.03638090549367472</v>
+        <v>-0.07281801844231212</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.008993454881275377</v>
+        <v>-0.09117609864296113</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
         <v>-0</v>
@@ -9780,7 +9780,7 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.02989385899019151</v>
+        <v>-0.1059165190650464</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -9789,10 +9789,10 @@
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.01021494927292516</v>
+        <v>0.03608075716246708</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.01933616188219326</v>
+        <v>0.08598920051560828</v>
       </c>
       <c r="CJ17" t="n">
         <v>-0</v>
@@ -9801,25 +9801,25 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.0002021315170799533</v>
+        <v>-0.2230589846646842</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.006881199366425569</v>
+        <v>0.17531060417505</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.02803817581634797</v>
+        <v>0.06222993581575119</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9828,25 +9828,25 @@
         <v>-0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.02229336698430819</v>
+        <v>-0.1045691078984927</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.006184657115176152</v>
+        <v>0.006140800636230638</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.0279594134279581</v>
+        <v>0.09383377204242571</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9861,19 +9861,19 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.01210890107323239</v>
+        <v>-0.02429771070690281</v>
       </c>
       <c r="DG17" t="n">
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.0104433278268914</v>
+        <v>-0.02079127372754791</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.003805924586018734</v>
+        <v>0.02348599961958348</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
@@ -9882,13 +9882,13 @@
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.02789640592226996</v>
+        <v>-0.09137101487089133</v>
       </c>
       <c r="DP17" t="n">
         <v>0</v>
@@ -9897,16 +9897,16 @@
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.02880624034901601</v>
+        <v>0.01826019203318983</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0261480629616661</v>
+        <v>0.09625465888438195</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV17" t="n">
         <v>-0</v>
@@ -9915,22 +9915,22 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.006299221443539146</v>
+        <v>0.03258435639705391</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.02702179783471992</v>
+        <v>-0.05956151214387194</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.01077363923906738</v>
+        <v>0.05856144337586889</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9939,64 +9939,64 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.0161834078165294</v>
+        <v>-0.03075575835699146</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0190889435468605</v>
+        <v>-0.0529689646509407</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.008616091625739248</v>
+        <v>0.05707129980580207</v>
       </c>
       <c r="EL17" t="n">
         <v>-0</v>
       </c>
       <c r="EM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-3.32959205691918e-05</v>
+        <v>-0.03404645699181105</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.01568123658661064</v>
+        <v>-0.05331391749991487</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0.0291336858628004</v>
+        <v>-0.08293603910332432</v>
       </c>
       <c r="EU17" t="n">
         <v>0</v>
       </c>
       <c r="EV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
         <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.01813252205631794</v>
+        <v>-0.1167571723845735</v>
       </c>
       <c r="EZ17" t="n">
         <v>0</v>
@@ -10005,13 +10005,13 @@
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.003363616887637702</v>
+        <v>0.008073237323698803</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.02792489609943506</v>
+        <v>0.07920740385161186</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
@@ -10023,7 +10023,7 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.02403887670226089</v>
+        <v>-0.08074588559766334</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
@@ -10032,25 +10032,25 @@
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.04098436695841654</v>
+        <v>0.05080159321179373</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01539176755738058</v>
+        <v>-0.01473747998767071</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.001885433809501707</v>
+        <v>-0.02429197959876679</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,43 +10059,43 @@
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.001371597360001756</v>
+        <v>0.001270735534074168</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01834722825024067</v>
+        <v>-0.01930960078890075</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.02459857039447088</v>
+        <v>-0.03987122832901713</v>
       </c>
       <c r="GA17" t="n">
         <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.02231485745684398</v>
+        <v>0.02479059824193582</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
